--- a/input/industry/IND_Hourly_load_profile.xlsx
+++ b/input/industry/IND_Hourly_load_profile.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{784B6716-0363-416A-89E5-27CBB2B5A233}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26687592-887C-49A7-BB17-A896D1934C01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29190" yWindow="690" windowWidth="27855" windowHeight="14820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7305" yWindow="3375" windowWidth="20175" windowHeight="13230" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -44,9 +44,6 @@
   </si>
   <si>
     <t>F1</t>
-  </si>
-  <si>
-    <t>German industrial electricity timeseries per subsector</t>
   </si>
   <si>
     <t>Unit:</t>
@@ -88,9 +85,6 @@
     <t>http://opendata.ffe.de/data/?_sft_energy_source=electric_energy&amp;_sft_project=demandregio,dynamis,extremos</t>
   </si>
   <si>
-    <t>Student Master Thesis used for electricity profiles</t>
-  </si>
-  <si>
     <t>Regener, Vincenz</t>
   </si>
   <si>
@@ -98,6 +92,12 @@
   </si>
   <si>
     <t>Modeling the German heat transition until 2050 – scenario studies on key technologies and legal framework</t>
+  </si>
+  <si>
+    <t>German industrial electricity load profiles per subsector</t>
+  </si>
+  <si>
+    <t>German industrial electricity load profiles</t>
   </si>
 </sst>
 </file>
@@ -70535,62 +70535,62 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" t="s">
         <v>6</v>
-      </c>
-      <c r="B1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B4" s="1"/>
       <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
         <v>11</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>12</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" t="s">
         <v>13</v>
       </c>
-      <c r="F4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>14</v>
-      </c>
-      <c r="H4" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
         <v>9</v>
       </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G5">
         <v>2020</v>
       </c>
       <c r="H5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -70601,10 +70601,10 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
